--- a/data/raw/cons_conf_sk.xlsx
+++ b/data/raw/cons_conf_sk.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,19 +421,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B2" t="n">
@@ -455,7 +441,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B3" t="n">
@@ -463,7 +449,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B4" t="n">
@@ -471,7 +457,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B5" t="n">
@@ -479,7 +465,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B6" t="n">
@@ -487,7 +473,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B7" t="n">
@@ -495,7 +481,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B8" t="n">
@@ -503,7 +489,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B9" t="n">
@@ -511,7 +497,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B10" t="n">
@@ -519,7 +505,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B11" t="n">
@@ -527,7 +513,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B12" t="n">
@@ -535,7 +521,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B13" t="n">
@@ -543,7 +529,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B14" t="n">
@@ -551,7 +537,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B15" t="n">
@@ -559,7 +545,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B16" t="n">
@@ -567,7 +553,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B17" t="n">
@@ -575,7 +561,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B18" t="n">
@@ -583,7 +569,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B19" t="n">
@@ -591,7 +577,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B20" t="n">
@@ -599,7 +585,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B21" t="n">
@@ -607,7 +593,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B22" t="n">
@@ -615,7 +601,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B23" t="n">
@@ -623,7 +609,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B24" t="n">
@@ -631,7 +617,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B25" t="n">
@@ -639,7 +625,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B26" t="n">
@@ -647,7 +633,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B27" t="n">
@@ -655,7 +641,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B28" t="n">
@@ -663,7 +649,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B29" t="n">
@@ -671,7 +657,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B30" t="n">
@@ -679,7 +665,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B31" t="n">
@@ -687,7 +673,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B32" t="n">
@@ -695,7 +681,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B33" t="n">
@@ -703,7 +689,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B34" t="n">
@@ -711,7 +697,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B35" t="n">
@@ -719,7 +705,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B36" t="n">
@@ -727,7 +713,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B37" t="n">
@@ -735,7 +721,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B38" t="n">
@@ -743,7 +729,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B39" t="n">
@@ -751,7 +737,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B40" t="n">
@@ -759,7 +745,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B41" t="n">
@@ -767,7 +753,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B42" t="n">
@@ -775,7 +761,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B43" t="n">
@@ -783,7 +769,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B44" t="n">
@@ -791,7 +777,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B45" t="n">
@@ -799,7 +785,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B46" t="n">
@@ -807,7 +793,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B47" t="n">
@@ -815,7 +801,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B48" t="n">
@@ -823,7 +809,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B49" t="n">
@@ -831,7 +817,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B50" t="n">
@@ -839,7 +825,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B51" t="n">
@@ -847,7 +833,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B52" t="n">
@@ -855,7 +841,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B53" t="n">
@@ -863,7 +849,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B54" t="n">
@@ -871,7 +857,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B55" t="n">
@@ -879,7 +865,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B56" t="n">
@@ -887,7 +873,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B57" t="n">
@@ -895,7 +881,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B58" t="n">
@@ -903,7 +889,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B59" t="n">
@@ -911,7 +897,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B60" t="n">
@@ -919,7 +905,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B61" t="n">
@@ -927,7 +913,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B62" t="n">
@@ -935,7 +921,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B63" t="n">
@@ -943,7 +929,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B64" t="n">
@@ -951,7 +937,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B65" t="n">
@@ -959,7 +945,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B66" t="n">
@@ -967,7 +953,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B67" t="n">
@@ -975,7 +961,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B68" t="n">
@@ -983,7 +969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B69" t="n">
@@ -991,7 +977,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B70" t="n">
@@ -999,7 +985,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B71" t="n">
@@ -1007,7 +993,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B72" t="n">
@@ -1015,7 +1001,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B73" t="n">
@@ -1023,7 +1009,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B74" t="n">
@@ -1031,7 +1017,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B75" t="n">
@@ -1039,7 +1025,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B76" t="n">
@@ -1047,7 +1033,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B77" t="n">
@@ -1055,7 +1041,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B78" t="n">
@@ -1063,7 +1049,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B79" t="n">
@@ -1071,7 +1057,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B80" t="n">
@@ -1079,7 +1065,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B81" t="n">
@@ -1087,7 +1073,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B82" t="n">
@@ -1095,7 +1081,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B83" t="n">
@@ -1103,7 +1089,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B84" t="n">
@@ -1111,7 +1097,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B85" t="n">
@@ -1119,7 +1105,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B86" t="n">
@@ -1127,7 +1113,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B87" t="n">
@@ -1135,7 +1121,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B88" t="n">
@@ -1143,7 +1129,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B89" t="n">
@@ -1151,7 +1137,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B90" t="n">
@@ -1159,7 +1145,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B91" t="n">
@@ -1167,7 +1153,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B92" t="n">
@@ -1175,7 +1161,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B93" t="n">
@@ -1183,7 +1169,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B94" t="n">
@@ -1191,7 +1177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B95" t="n">
@@ -1199,7 +1185,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B96" t="n">
@@ -1207,7 +1193,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B97" t="n">
@@ -1215,7 +1201,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B98" t="n">
@@ -1223,7 +1209,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B99" t="n">
@@ -1231,7 +1217,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B100" t="n">
@@ -1239,7 +1225,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B101" t="n">
@@ -1247,7 +1233,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B102" t="n">
@@ -1255,7 +1241,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B103" t="n">
@@ -1263,7 +1249,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B104" t="n">
@@ -1271,7 +1257,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B105" t="n">
@@ -1279,7 +1265,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B106" t="n">
@@ -1287,7 +1273,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B107" t="n">
@@ -1295,7 +1281,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B108" t="n">
@@ -1303,7 +1289,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B109" t="n">
@@ -1311,7 +1297,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B110" t="n">
@@ -1319,7 +1305,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B111" t="n">
@@ -1327,7 +1313,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B112" t="n">
@@ -1335,7 +1321,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B113" t="n">
@@ -1343,7 +1329,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B114" t="n">
@@ -1351,7 +1337,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B115" t="n">
@@ -1359,7 +1345,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B116" t="n">
@@ -1367,7 +1353,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B117" t="n">
@@ -1375,7 +1361,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B118" t="n">
@@ -1383,7 +1369,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B119" t="n">
@@ -1391,7 +1377,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B120" t="n">
@@ -1399,7 +1385,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B121" t="n">
@@ -1407,7 +1393,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B122" t="n">
@@ -1415,7 +1401,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B123" t="n">
@@ -1423,7 +1409,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B124" t="n">
@@ -1431,7 +1417,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B125" t="n">
@@ -1439,7 +1425,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B126" t="n">
@@ -1447,7 +1433,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B127" t="n">
@@ -1455,7 +1441,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B128" t="n">
@@ -1463,7 +1449,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B129" t="n">
@@ -1471,7 +1457,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B130" t="n">
@@ -1479,7 +1465,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B131" t="n">
@@ -1487,7 +1473,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B132" t="n">
@@ -1495,7 +1481,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B133" t="n">
@@ -1503,7 +1489,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B134" t="n">
@@ -1511,7 +1497,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B135" t="n">
@@ -1519,7 +1505,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B136" t="n">
@@ -1527,7 +1513,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B137" t="n">
@@ -1535,7 +1521,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B138" t="n">
@@ -1543,7 +1529,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B139" t="n">
@@ -1551,7 +1537,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B140" t="n">
@@ -1559,7 +1545,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B141" t="n">
@@ -1567,7 +1553,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B142" t="n">
@@ -1575,7 +1561,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B143" t="n">
@@ -1583,7 +1569,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B144" t="n">
@@ -1591,7 +1577,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B145" t="n">
@@ -1599,7 +1585,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B146" t="n">
@@ -1607,7 +1593,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B147" t="n">
@@ -1615,7 +1601,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B148" t="n">
@@ -1623,7 +1609,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B149" t="n">
@@ -1631,7 +1617,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B150" t="n">
@@ -1639,7 +1625,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B151" t="n">
@@ -1647,7 +1633,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B152" t="n">
@@ -1655,7 +1641,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B153" t="n">
@@ -1663,7 +1649,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B154" t="n">
@@ -1671,7 +1657,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B155" t="n">
@@ -1679,7 +1665,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B156" t="n">
@@ -1687,7 +1673,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B157" t="n">
@@ -1695,7 +1681,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B158" t="n">
@@ -1703,7 +1689,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B159" t="n">
@@ -1711,7 +1697,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B160" t="n">
@@ -1719,7 +1705,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B161" t="n">
@@ -1727,7 +1713,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B162" t="n">
@@ -1735,7 +1721,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B163" t="n">
@@ -1743,7 +1729,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B164" t="n">
@@ -1751,7 +1737,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B165" t="n">
@@ -1759,7 +1745,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B166" t="n">
@@ -1767,7 +1753,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B167" t="n">
@@ -1775,7 +1761,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B168" t="n">
@@ -1783,7 +1769,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B169" t="n">
@@ -1791,7 +1777,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B170" t="n">
@@ -1799,7 +1785,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B171" t="n">
@@ -1807,7 +1793,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B172" t="n">
@@ -1815,7 +1801,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B173" t="n">
@@ -1823,7 +1809,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B174" t="n">
@@ -1831,7 +1817,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B175" t="n">
@@ -1839,7 +1825,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B176" t="n">
@@ -1847,7 +1833,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B177" t="n">
@@ -1855,7 +1841,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B178" t="n">
@@ -1863,7 +1849,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B179" t="n">
@@ -1871,7 +1857,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B180" t="n">
@@ -1879,7 +1865,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B181" t="n">
@@ -1887,7 +1873,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B182" t="n">
@@ -1895,7 +1881,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B183" t="n">
@@ -1903,7 +1889,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B184" t="n">
@@ -1911,7 +1897,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B185" t="n">
@@ -1919,7 +1905,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B186" t="n">
@@ -1927,7 +1913,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B187" t="n">
@@ -1935,7 +1921,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B188" t="n">
@@ -1943,7 +1929,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B189" t="n">
@@ -1951,7 +1937,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B190" t="n">
@@ -1959,7 +1945,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B191" t="n">
@@ -1967,7 +1953,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B192" t="n">
@@ -1975,7 +1961,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B193" t="n">
@@ -1983,7 +1969,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B194" t="n">
@@ -1991,7 +1977,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B195" t="n">
@@ -1999,7 +1985,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B196" t="n">
@@ -2007,7 +1993,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B197" t="n">
@@ -2015,7 +2001,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B198" t="n">
@@ -2023,7 +2009,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B199" t="n">
@@ -2031,7 +2017,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B200" t="n">
@@ -2039,7 +2025,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B201" t="n">
@@ -2047,7 +2033,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B202" t="n">
@@ -2055,7 +2041,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B203" t="n">
@@ -2063,7 +2049,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B204" t="n">
@@ -2071,7 +2057,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B205" t="n">
@@ -2079,7 +2065,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B206" t="n">
@@ -2087,7 +2073,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B207" t="n">
@@ -2095,7 +2081,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B208" t="n">
@@ -2103,7 +2089,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B209" t="n">
@@ -2111,7 +2097,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B210" t="n">
@@ -2119,7 +2105,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B211" t="n">
@@ -2127,7 +2113,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B212" t="n">
@@ -2135,7 +2121,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B213" t="n">
@@ -2143,7 +2129,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B214" t="n">
@@ -2151,7 +2137,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B215" t="n">
@@ -2159,7 +2145,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B216" t="n">
@@ -2167,7 +2153,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B217" t="n">
@@ -2175,7 +2161,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B218" t="n">
@@ -2183,7 +2169,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B219" t="n">
@@ -2191,7 +2177,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B220" t="n">
@@ -2199,7 +2185,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B221" t="n">
@@ -2207,7 +2193,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B222" t="n">
@@ -2215,7 +2201,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B223" t="n">
@@ -2223,7 +2209,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B224" t="n">
@@ -2231,7 +2217,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B225" t="n">
@@ -2239,7 +2225,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B226" t="n">
@@ -2247,7 +2233,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B227" t="n">
@@ -2255,7 +2241,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B228" t="n">
@@ -2263,7 +2249,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B229" t="n">
@@ -2271,7 +2257,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B230" t="n">
@@ -2279,7 +2265,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B231" t="n">
@@ -2287,7 +2273,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B232" t="n">
@@ -2295,7 +2281,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B233" t="n">
@@ -2303,7 +2289,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B234" t="n">
@@ -2311,7 +2297,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B235" t="n">
@@ -2319,7 +2305,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B236" t="n">
@@ -2327,7 +2313,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B237" t="n">
@@ -2335,7 +2321,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B238" t="n">
@@ -2343,7 +2329,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B239" t="n">
@@ -2351,7 +2337,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B240" t="n">
@@ -2359,7 +2345,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B241" t="n">
@@ -2367,7 +2353,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B242" t="n">
@@ -2375,7 +2361,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B243" t="n">
@@ -2383,7 +2369,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B244" t="n">
@@ -2391,7 +2377,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B245" t="n">
@@ -2399,7 +2385,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B246" t="n">
@@ -2407,7 +2393,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B247" t="n">
@@ -2415,7 +2401,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B248" t="n">
@@ -2423,7 +2409,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B249" t="n">
@@ -2431,7 +2417,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B250" t="n">
@@ -2439,7 +2425,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B251" t="n">
@@ -2447,7 +2433,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B252" t="n">
@@ -2455,7 +2441,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B253" t="n">
@@ -2463,7 +2449,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B254" t="n">
@@ -2471,7 +2457,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B255" t="n">
@@ -2479,7 +2465,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B256" t="n">
@@ -2487,7 +2473,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B257" t="n">
@@ -2495,7 +2481,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B258" t="n">
@@ -2503,7 +2489,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B259" t="n">
@@ -2511,7 +2497,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B260" t="n">
@@ -2519,7 +2505,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B261" t="n">
@@ -2527,7 +2513,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B262" t="n">
@@ -2535,7 +2521,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B263" t="n">
@@ -2543,7 +2529,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B264" t="n">
@@ -2551,7 +2537,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B265" t="n">
@@ -2559,7 +2545,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B266" t="n">
@@ -2567,7 +2553,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B267" t="n">
@@ -2575,7 +2561,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B268" t="n">
@@ -2583,7 +2569,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B269" t="n">
@@ -2591,7 +2577,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B270" t="n">
@@ -2599,7 +2585,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B271" t="n">
@@ -2607,7 +2593,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B272" t="n">
@@ -2615,7 +2601,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B273" t="n">
@@ -2623,7 +2609,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B274" t="n">
@@ -2631,7 +2617,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B275" t="n">
@@ -2639,7 +2625,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B276" t="n">
@@ -2647,7 +2633,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B277" t="n">
@@ -2655,7 +2641,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B278" t="n">
@@ -2663,7 +2649,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B279" t="n">
@@ -2671,7 +2657,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B280" t="n">
@@ -2679,7 +2665,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B281" t="n">
@@ -2687,7 +2673,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B282" t="n">
@@ -2695,7 +2681,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B283" t="n">
@@ -2703,7 +2689,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B284" t="n">
@@ -2711,7 +2697,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B285" t="n">
@@ -2719,7 +2705,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B286" t="n">
@@ -2727,7 +2713,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B287" t="n">
@@ -2735,7 +2721,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B288" t="n">
@@ -2743,7 +2729,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B289" t="n">
@@ -2751,7 +2737,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B290" t="n">
@@ -2759,7 +2745,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B291" t="n">
@@ -2767,7 +2753,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B292" t="n">
@@ -2775,7 +2761,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B293" t="n">
@@ -2783,7 +2769,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B294" t="n">
@@ -2791,7 +2777,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B295" t="n">
@@ -2799,7 +2785,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B296" t="n">
@@ -2807,7 +2793,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B297" t="n">
@@ -2815,7 +2801,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B298" t="n">
@@ -2823,7 +2809,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B299" t="n">
@@ -2831,7 +2817,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B300" t="n">
@@ -2839,7 +2825,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B301" t="n">
@@ -2847,7 +2833,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B302" t="n">
@@ -2855,7 +2841,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B303" t="n">
@@ -2863,7 +2849,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B304" t="n">
@@ -2871,7 +2857,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B305" t="n">
@@ -2879,7 +2865,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B306" t="n">
@@ -2887,7 +2873,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B307" t="n">
@@ -2895,7 +2881,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B308" t="n">
@@ -2903,7 +2889,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B309" t="n">
@@ -2911,7 +2897,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B310" t="n">
@@ -2919,7 +2905,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B311" t="n">
@@ -2927,7 +2913,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B312" t="n">
@@ -2935,7 +2921,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B313" t="n">
@@ -2943,7 +2929,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B314" t="n">
@@ -2951,7 +2937,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B315" t="n">
@@ -2959,7 +2945,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B316" t="n">
@@ -2967,7 +2953,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B317" t="n">
@@ -2975,7 +2961,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B318" t="n">
@@ -2983,7 +2969,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B319" t="n">
@@ -2991,7 +2977,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B320" t="n">
@@ -2999,7 +2985,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B321" t="n">
@@ -3007,7 +2993,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B322" t="n">
@@ -3015,7 +3001,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B323" t="n">
@@ -3023,7 +3009,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B324" t="n">
@@ -3031,7 +3017,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B325" t="n">
@@ -3039,7 +3025,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B326" t="n">
@@ -3047,7 +3033,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B327" t="n">
@@ -3055,7 +3041,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B328" t="n">
@@ -3063,7 +3049,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B329" t="n">
@@ -3071,7 +3057,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B330" t="n">
@@ -3079,7 +3065,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B331" t="n">
@@ -3087,7 +3073,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B332" t="n">
@@ -3095,7 +3081,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B333" t="n">
@@ -3103,7 +3089,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B334" t="n">
@@ -3111,7 +3097,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B335" t="n">
@@ -3119,7 +3105,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B336" t="n">
@@ -3127,7 +3113,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B337" t="n">
@@ -3135,7 +3121,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B338" t="n">
@@ -3143,7 +3129,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B339" t="n">
@@ -3151,7 +3137,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B340" t="n">
@@ -3159,7 +3145,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B341" t="n">
@@ -3167,7 +3153,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B342" t="n">
@@ -3175,7 +3161,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B343" t="n">
@@ -3183,7 +3169,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B344" t="n">
@@ -3191,7 +3177,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B345" t="n">
@@ -3199,7 +3185,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B346" t="n">
@@ -3207,7 +3193,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B347" t="n">
@@ -3215,7 +3201,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B348" t="n">
@@ -3223,7 +3209,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B349" t="n">
@@ -3231,7 +3217,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B350" t="n">
@@ -3239,7 +3225,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B351" t="n">
@@ -3247,7 +3233,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B352" t="n">
@@ -3255,7 +3241,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B353" t="n">
@@ -3263,7 +3249,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B354" t="n">
@@ -3271,7 +3257,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B355" t="n">
@@ -3279,7 +3265,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B356" t="n">
@@ -3287,7 +3273,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B357" t="n">
@@ -3295,7 +3281,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B358" t="n">
@@ -3303,7 +3289,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B359" t="n">
@@ -3311,7 +3297,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B360" t="n">
@@ -3319,7 +3305,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B361" t="n">
@@ -3327,7 +3313,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B362" t="n">
@@ -3335,7 +3321,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B363" t="n">
@@ -3343,7 +3329,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B364" t="n">
@@ -3351,7 +3337,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B365" t="n">
@@ -3359,7 +3345,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B366" t="n">
@@ -3367,7 +3353,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B367" t="n">
@@ -3375,7 +3361,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B368" t="n">
@@ -3383,7 +3369,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B369" t="n">
@@ -3391,7 +3377,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B370" t="n">
@@ -3399,7 +3385,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B371" t="n">
@@ -3407,7 +3393,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B372" t="n">
@@ -3415,7 +3401,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B373" t="n">
@@ -3423,7 +3409,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B374" t="n">
@@ -3431,7 +3417,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B375" t="n">
@@ -3439,7 +3425,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B376" t="n">
@@ -3447,7 +3433,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B377" t="n">
@@ -3455,7 +3441,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B378" t="n">
@@ -3463,7 +3449,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B379" t="n">
@@ -3471,7 +3457,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B380" t="n">
@@ -3479,7 +3465,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B381" t="n">
@@ -3487,7 +3473,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B382" t="n">
@@ -3495,7 +3481,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B383" t="n">
@@ -3503,7 +3489,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B384" t="n">
@@ -3511,7 +3497,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B385" t="n">
@@ -3519,7 +3505,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B386" t="n">
@@ -3527,7 +3513,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B387" t="n">
@@ -3535,7 +3521,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B388" t="n">
@@ -3543,7 +3529,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B389" t="n">
@@ -3551,7 +3537,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B390" t="n">
@@ -3559,7 +3545,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B391" t="n">
@@ -3567,7 +3553,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B392" t="n">
@@ -3575,7 +3561,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B393" t="n">
@@ -3583,7 +3569,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B394" t="n">
@@ -3591,7 +3577,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B395" t="n">
@@ -3599,7 +3585,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B396" t="n">
